--- a/research/traditional_assets/database/data/kenya/kenya_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_real_estate_development.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.212</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.6228813559322034</v>
+        <v>-0.0226537216828479</v>
       </c>
       <c r="H2">
-        <v>-0.6228813559322034</v>
+        <v>-0.0226537216828479</v>
       </c>
       <c r="I2">
-        <v>-0.7966101694915254</v>
+        <v>-0.04368932038834952</v>
       </c>
       <c r="J2">
-        <v>-0.7966101694915254</v>
+        <v>-0.04368932038834952</v>
       </c>
       <c r="K2">
-        <v>-2.1</v>
+        <v>-2.57</v>
       </c>
       <c r="L2">
-        <v>-0.8898305084745763</v>
+        <v>-0.8317152103559871</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.095</v>
+        <v>0.02</v>
       </c>
       <c r="V2">
-        <v>0.06643356643356643</v>
+        <v>0.01904761904761905</v>
       </c>
       <c r="W2">
-        <v>0.1337579617834395</v>
+        <v>0.1596273291925465</v>
       </c>
       <c r="X2">
-        <v>0.4935847243659957</v>
+        <v>1.101015008999505</v>
       </c>
       <c r="Y2">
-        <v>-0.3598267625825562</v>
+        <v>-0.9413876798069589</v>
       </c>
       <c r="Z2">
-        <v>-0.149869816472979</v>
+        <v>1.980769230769234</v>
       </c>
       <c r="AA2">
-        <v>0.1193878199022036</v>
+        <v>-0.08653846153846166</v>
       </c>
       <c r="AB2">
-        <v>0.08183093061575922</v>
+        <v>0.1415735856981875</v>
       </c>
       <c r="AC2">
-        <v>0.03755688928644436</v>
+        <v>-0.2281120472366491</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="AG2">
-        <v>17.905</v>
+        <v>18.88</v>
       </c>
       <c r="AH2">
-        <v>0.9264024704065877</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="AI2">
-        <v>-3.461538461538462</v>
+        <v>-5.108108108108103</v>
       </c>
       <c r="AJ2">
-        <v>0.9260408585466771</v>
+        <v>0.9473156046161565</v>
       </c>
       <c r="AK2">
-        <v>-3.381491973559964</v>
+        <v>-5.075268817204297</v>
       </c>
       <c r="AL2">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="AM2">
-        <v>1.52</v>
+        <v>2.65</v>
+      </c>
+      <c r="AN2">
+        <v>-269.9999999999999</v>
       </c>
       <c r="AO2">
-        <v>-1.236842105263158</v>
+        <v>-0.0509433962264151</v>
+      </c>
+      <c r="AP2">
+        <v>-269.7142857142857</v>
       </c>
       <c r="AQ2">
-        <v>-1.236842105263158</v>
+        <v>-0.0509433962264151</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.212</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.6228813559322034</v>
+        <v>-0.0226537216828479</v>
       </c>
       <c r="H3">
-        <v>-0.6228813559322034</v>
+        <v>-0.0226537216828479</v>
       </c>
       <c r="I3">
-        <v>-0.7966101694915254</v>
+        <v>-0.04368932038834952</v>
       </c>
       <c r="J3">
-        <v>-0.7966101694915254</v>
+        <v>-0.04368932038834952</v>
       </c>
       <c r="K3">
-        <v>-2.1</v>
+        <v>-2.57</v>
       </c>
       <c r="L3">
-        <v>-0.8898305084745763</v>
+        <v>-0.8317152103559871</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,67 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.095</v>
+        <v>0.02</v>
       </c>
       <c r="V3">
-        <v>0.06643356643356643</v>
+        <v>0.01904761904761905</v>
       </c>
       <c r="W3">
-        <v>0.1337579617834395</v>
+        <v>0.1596273291925465</v>
       </c>
       <c r="X3">
-        <v>0.4935847243659957</v>
+        <v>1.101015008999505</v>
       </c>
       <c r="Y3">
-        <v>-0.3598267625825562</v>
+        <v>-0.9413876798069589</v>
       </c>
       <c r="Z3">
-        <v>-0.149869816472979</v>
+        <v>1.980769230769234</v>
       </c>
       <c r="AA3">
-        <v>0.1193878199022036</v>
+        <v>-0.08653846153846166</v>
       </c>
       <c r="AB3">
-        <v>0.08183093061575922</v>
+        <v>0.1415735856981875</v>
       </c>
       <c r="AC3">
-        <v>0.03755688928644436</v>
+        <v>-0.2281120472366491</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="AG3">
-        <v>17.905</v>
+        <v>18.88</v>
       </c>
       <c r="AH3">
-        <v>0.9264024704065877</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="AI3">
-        <v>-3.461538461538462</v>
+        <v>-5.108108108108103</v>
       </c>
       <c r="AJ3">
-        <v>0.9260408585466771</v>
+        <v>0.9473156046161565</v>
       </c>
       <c r="AK3">
-        <v>-3.381491973559964</v>
+        <v>-5.075268817204297</v>
       </c>
       <c r="AL3">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="AM3">
-        <v>1.52</v>
+        <v>2.65</v>
+      </c>
+      <c r="AN3">
+        <v>-269.9999999999999</v>
       </c>
       <c r="AO3">
-        <v>-1.236842105263158</v>
+        <v>-0.0509433962264151</v>
+      </c>
+      <c r="AP3">
+        <v>-269.7142857142857</v>
       </c>
       <c r="AQ3">
-        <v>-1.236842105263158</v>
+        <v>-0.0509433962264151</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_real_estate_development.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09470000000000001</v>
+        <v>-0.0201</v>
       </c>
       <c r="G2">
-        <v>-0.0226537216828479</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="H2">
-        <v>-0.0226537216828479</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="I2">
-        <v>-0.04368932038834952</v>
+        <v>-0.1020833333333333</v>
       </c>
       <c r="J2">
-        <v>-0.04368932038834952</v>
+        <v>-0.1020833333333333</v>
       </c>
       <c r="K2">
-        <v>-2.57</v>
+        <v>-0.486</v>
       </c>
       <c r="L2">
-        <v>-0.8317152103559871</v>
+        <v>-0.253125</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,52 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.01904761904761905</v>
-      </c>
-      <c r="W2">
-        <v>0.1596273291925465</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1.101015008999505</v>
-      </c>
-      <c r="Y2">
-        <v>-0.9413876798069589</v>
-      </c>
-      <c r="Z2">
-        <v>1.980769230769234</v>
-      </c>
-      <c r="AA2">
-        <v>-0.08653846153846166</v>
+        <v>0.1016740211508091</v>
       </c>
       <c r="AB2">
-        <v>0.1415735856981875</v>
-      </c>
-      <c r="AC2">
-        <v>-0.2281120472366491</v>
+        <v>0.1016740211508091</v>
       </c>
       <c r="AD2">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="AI2">
-        <v>-5.108108108108103</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.9473156046161565</v>
-      </c>
-      <c r="AK2">
-        <v>-5.075268817204297</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.65</v>
+        <v>0.327</v>
       </c>
       <c r="AM2">
-        <v>2.65</v>
+        <v>0.327</v>
       </c>
       <c r="AN2">
-        <v>-269.9999999999999</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-0.0509433962264151</v>
+        <v>-0.599388379204893</v>
       </c>
       <c r="AP2">
-        <v>-269.7142857142857</v>
+        <v>-0</v>
       </c>
       <c r="AQ2">
-        <v>-0.0509433962264151</v>
+        <v>-0.599388379204893</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09470000000000001</v>
+        <v>-0.0201</v>
       </c>
       <c r="G3">
-        <v>-0.0226537216828479</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="H3">
-        <v>-0.0226537216828479</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.04368932038834952</v>
+        <v>-0.1020833333333333</v>
       </c>
       <c r="J3">
-        <v>-0.04368932038834952</v>
+        <v>-0.1020833333333333</v>
       </c>
       <c r="K3">
-        <v>-2.57</v>
+        <v>-0.486</v>
       </c>
       <c r="L3">
-        <v>-0.8317152103559871</v>
+        <v>-0.253125</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +737,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.01904761904761905</v>
-      </c>
-      <c r="W3">
-        <v>0.1596273291925465</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.101015008999505</v>
-      </c>
-      <c r="Y3">
-        <v>-0.9413876798069589</v>
-      </c>
-      <c r="Z3">
-        <v>1.980769230769234</v>
-      </c>
-      <c r="AA3">
-        <v>-0.08653846153846166</v>
+        <v>0.1016740211508091</v>
       </c>
       <c r="AB3">
-        <v>0.1415735856981875</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2281120472366491</v>
+        <v>0.1016740211508091</v>
       </c>
       <c r="AD3">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="AI3">
-        <v>-5.108108108108103</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.9473156046161565</v>
-      </c>
-      <c r="AK3">
-        <v>-5.075268817204297</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>2.65</v>
+        <v>0.327</v>
       </c>
       <c r="AM3">
-        <v>2.65</v>
+        <v>0.327</v>
       </c>
       <c r="AN3">
-        <v>-269.9999999999999</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-0.0509433962264151</v>
+        <v>-0.599388379204893</v>
       </c>
       <c r="AP3">
-        <v>-269.7142857142857</v>
+        <v>-0</v>
       </c>
       <c r="AQ3">
-        <v>-0.0509433962264151</v>
+        <v>-0.599388379204893</v>
       </c>
     </row>
   </sheetData>
